--- a/W2M TH Contract Rate 2027 - Transfer Service.xlsx
+++ b/W2M TH Contract Rate 2027 - Transfer Service.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CONTRACT R. 2027 1. W2M TH\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CONTRACT R. 2027 1. W2M TH\+4_Website Upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DA3B29-5399-4B0F-A71A-FDDA4370954E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041619BB-D295-47E7-88A5-F5883EBB0DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transfer Contract Rates" sheetId="1" r:id="rId1"/>
@@ -550,7 +550,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -611,6 +611,17 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -794,7 +805,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -814,31 +825,25 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -846,22 +851,21 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -872,6 +876,14 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1099,1294 +1111,1447 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="12"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="15"/>
     </row>
     <row r="2" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="12"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="15"/>
     </row>
     <row r="3" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="15"/>
     </row>
     <row r="5" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="12"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="15"/>
     </row>
     <row r="6" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="15" t="s">
+      <c r="B6" s="15"/>
+      <c r="C6" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="15" t="s">
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="12"/>
+      <c r="H6" s="15"/>
       <c r="I6" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="12"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="15"/>
     </row>
     <row r="8" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="7" t="s">
+      <c r="B8" s="10"/>
+      <c r="C8" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="9"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="10"/>
       <c r="I8" s="4">
         <v>900</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="7" t="s">
+      <c r="B9" s="10"/>
+      <c r="C9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="9"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="10"/>
       <c r="I9" s="4">
         <v>1800</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="7" t="s">
+      <c r="B10" s="10"/>
+      <c r="C10" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="9"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="10"/>
       <c r="I10" s="4">
         <v>1800</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="7" t="s">
+      <c r="B11" s="10"/>
+      <c r="C11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="9"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="10"/>
       <c r="I11" s="4">
         <v>2200</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="7" t="s">
+      <c r="B12" s="10"/>
+      <c r="C12" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="9"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="10"/>
       <c r="I12" s="4">
         <v>2550</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="7" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" s="9"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="10"/>
       <c r="I13" s="4">
         <v>3500</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="7" t="s">
+      <c r="B14" s="10"/>
+      <c r="C14" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="9"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="10"/>
       <c r="I14" s="4">
         <v>4800</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="7" t="s">
+      <c r="B15" s="10"/>
+      <c r="C15" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" s="9"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="10"/>
       <c r="I15" s="4">
         <v>4800</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="7" t="s">
+      <c r="B16" s="10"/>
+      <c r="C16" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" s="9"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="10"/>
       <c r="I16" s="4">
         <v>5450</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="7" t="s">
+      <c r="B17" s="10"/>
+      <c r="C17" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H17" s="9"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="10"/>
       <c r="I17" s="4">
         <v>6400</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="12"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="15"/>
     </row>
     <row r="19" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="7" t="s">
+      <c r="B19" s="10"/>
+      <c r="C19" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H19" s="9"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="10"/>
       <c r="I19" s="4">
         <v>1150</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="7" t="s">
+      <c r="B20" s="10"/>
+      <c r="C20" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H20" s="9"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="10"/>
       <c r="I20" s="4">
         <v>2550</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="7" t="s">
+      <c r="B21" s="10"/>
+      <c r="C21" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" s="9"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="10"/>
       <c r="I21" s="4">
         <v>2850</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="7" t="s">
+      <c r="B22" s="10"/>
+      <c r="C22" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="9"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="10"/>
       <c r="I22" s="4">
         <v>2850</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="7" t="s">
+      <c r="B23" s="10"/>
+      <c r="C23" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H23" s="9"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="10"/>
       <c r="I23" s="4">
         <v>3100</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="7" t="s">
+      <c r="B24" s="10"/>
+      <c r="C24" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H24" s="9"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="10"/>
       <c r="I24" s="4">
         <v>3750</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="7" t="s">
+      <c r="B25" s="10"/>
+      <c r="C25" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H25" s="9"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25" s="10"/>
       <c r="I25" s="4">
         <v>4800</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="12"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="15"/>
     </row>
     <row r="27" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="7" t="s">
+      <c r="B27" s="10"/>
+      <c r="C27" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H27" s="9"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="10"/>
       <c r="I27" s="4">
         <v>1400</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="7" t="s">
+      <c r="B28" s="10"/>
+      <c r="C28" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H28" s="9"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="10"/>
       <c r="I28" s="4">
         <v>1400</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="7" t="s">
+      <c r="B29" s="10"/>
+      <c r="C29" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H29" s="9"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="10"/>
       <c r="I29" s="4">
         <v>1400</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="7" t="s">
+      <c r="B30" s="10"/>
+      <c r="C30" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H30" s="9"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="10"/>
       <c r="I30" s="4">
         <v>2950</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="7" t="s">
+      <c r="B31" s="10"/>
+      <c r="C31" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H31" s="9"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="10"/>
       <c r="I31" s="4">
         <v>3050</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="7" t="s">
+      <c r="B32" s="10"/>
+      <c r="C32" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H32" s="9"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="10"/>
       <c r="I32" s="4">
         <v>2600</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="7" t="s">
+      <c r="B33" s="10"/>
+      <c r="C33" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H33" s="9"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="10"/>
       <c r="I33" s="4">
         <v>3650</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="7" t="s">
+      <c r="B34" s="10"/>
+      <c r="C34" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H34" s="9"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="10"/>
       <c r="I34" s="4">
         <v>3950</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="7" t="s">
+      <c r="B35" s="10"/>
+      <c r="C35" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H35" s="9"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" s="10"/>
       <c r="I35" s="4">
         <v>3950</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="7" t="s">
+      <c r="B36" s="10"/>
+      <c r="C36" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H36" s="9"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" s="10"/>
       <c r="I36" s="4">
         <v>3650</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="12"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="15"/>
     </row>
     <row r="38" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="7" t="s">
+      <c r="B38" s="10"/>
+      <c r="C38" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H38" s="9"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H38" s="10"/>
       <c r="I38" s="4">
         <v>1450</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="7" t="s">
+      <c r="B39" s="10"/>
+      <c r="C39" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H39" s="9"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" s="10"/>
       <c r="I39" s="4">
         <v>1450</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="7" t="s">
+      <c r="B40" s="10"/>
+      <c r="C40" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H40" s="9"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" s="10"/>
       <c r="I40" s="4">
         <v>1450</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="7" t="s">
+      <c r="B41" s="10"/>
+      <c r="C41" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H41" s="9"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41" s="10"/>
       <c r="I41" s="4">
         <v>1450</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="7" t="s">
+      <c r="B42" s="10"/>
+      <c r="C42" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H42" s="9"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42" s="10"/>
       <c r="I42" s="4">
         <v>1450</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="7" t="s">
+      <c r="B43" s="10"/>
+      <c r="C43" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H43" s="9"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="10"/>
       <c r="I43" s="4">
         <v>1450</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="7" t="s">
+      <c r="B44" s="10"/>
+      <c r="C44" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H44" s="9"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="10"/>
       <c r="I44" s="4">
         <v>1450</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="13" t="s">
+      <c r="A45" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="7" t="s">
+      <c r="B45" s="10"/>
+      <c r="C45" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H45" s="9"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" s="10"/>
       <c r="I45" s="4">
         <v>1450</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="7" t="s">
+      <c r="B46" s="10"/>
+      <c r="C46" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H46" s="9"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46" s="10"/>
       <c r="I46" s="4">
         <v>1450</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B47" s="9"/>
-      <c r="C47" s="7" t="s">
+      <c r="B47" s="10"/>
+      <c r="C47" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H47" s="9"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" s="10"/>
       <c r="I47" s="4">
         <v>1450</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="13" t="s">
+      <c r="A48" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B48" s="9"/>
-      <c r="C48" s="7" t="s">
+      <c r="B48" s="10"/>
+      <c r="C48" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H48" s="9"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" s="10"/>
       <c r="I48" s="4">
         <v>1450</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="13" t="s">
+      <c r="A49" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B49" s="9"/>
-      <c r="C49" s="7" t="s">
+      <c r="B49" s="10"/>
+      <c r="C49" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H49" s="9"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H49" s="10"/>
       <c r="I49" s="4">
         <v>1450</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="13" t="s">
+      <c r="A50" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B50" s="9"/>
-      <c r="C50" s="7" t="s">
+      <c r="B50" s="10"/>
+      <c r="C50" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H50" s="9"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50" s="10"/>
       <c r="I50" s="4">
         <v>4150</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B51" s="9"/>
-      <c r="C51" s="7" t="s">
+      <c r="B51" s="10"/>
+      <c r="C51" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H51" s="9"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H51" s="10"/>
       <c r="I51" s="4">
         <v>4950</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="13" t="s">
+      <c r="A52" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B52" s="9"/>
-      <c r="C52" s="7" t="s">
+      <c r="B52" s="10"/>
+      <c r="C52" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H52" s="9"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H52" s="10"/>
       <c r="I52" s="4">
         <v>4700</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="10" t="s">
+      <c r="A53" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="12"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="15"/>
     </row>
     <row r="54" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B54" s="9"/>
-      <c r="C54" s="7" t="s">
+      <c r="B54" s="10"/>
+      <c r="C54" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H54" s="9"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H54" s="10"/>
       <c r="I54" s="4">
         <v>1300</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="13" t="s">
+      <c r="A55" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B55" s="9"/>
-      <c r="C55" s="7" t="s">
+      <c r="B55" s="10"/>
+      <c r="C55" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H55" s="9"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H55" s="10"/>
       <c r="I55" s="4">
         <v>1350</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="13" t="s">
+      <c r="A56" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="9"/>
-      <c r="C56" s="7" t="s">
+      <c r="B56" s="10"/>
+      <c r="C56" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H56" s="9"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H56" s="10"/>
       <c r="I56" s="4">
         <v>1450</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="13" t="s">
+      <c r="A57" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B57" s="9"/>
-      <c r="C57" s="7" t="s">
+      <c r="B57" s="10"/>
+      <c r="C57" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H57" s="9"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H57" s="10"/>
       <c r="I57" s="4">
         <v>3350</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B58" s="9"/>
-      <c r="C58" s="7" t="s">
+      <c r="B58" s="10"/>
+      <c r="C58" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H58" s="9"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58" s="10"/>
       <c r="I58" s="4">
         <v>4700</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B59" s="9"/>
-      <c r="C59" s="7" t="s">
+      <c r="B59" s="10"/>
+      <c r="C59" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H59" s="9"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H59" s="10"/>
       <c r="I59" s="4">
         <v>4700</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="13" t="s">
+      <c r="A60" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B60" s="9"/>
-      <c r="C60" s="7" t="s">
+      <c r="B60" s="10"/>
+      <c r="C60" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H60" s="9"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="10"/>
+      <c r="G60" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H60" s="10"/>
       <c r="I60" s="4">
         <v>4150</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="13" t="s">
+      <c r="A61" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B61" s="9"/>
-      <c r="C61" s="7" t="s">
+      <c r="B61" s="10"/>
+      <c r="C61" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H61" s="9"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H61" s="10"/>
       <c r="I61" s="4">
         <v>4150</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="63" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="16" t="s">
+      <c r="A63" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="B63" s="17"/>
-      <c r="C63" s="17"/>
-      <c r="D63" s="17"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="17"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="17"/>
-      <c r="I63" s="17"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="8"/>
+      <c r="I63" s="8"/>
     </row>
     <row r="64" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="18" t="s">
+      <c r="A64" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B64" s="17"/>
-      <c r="C64" s="17"/>
-      <c r="D64" s="17"/>
-      <c r="E64" s="17"/>
-      <c r="F64" s="17"/>
-      <c r="G64" s="17"/>
-      <c r="H64" s="17"/>
-      <c r="I64" s="17"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8"/>
+      <c r="I64" s="8"/>
     </row>
     <row r="65" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="18" t="s">
+      <c r="A65" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B65" s="17"/>
-      <c r="C65" s="17"/>
-      <c r="D65" s="17"/>
-      <c r="E65" s="17"/>
-      <c r="F65" s="17"/>
-      <c r="G65" s="17"/>
-      <c r="H65" s="17"/>
-      <c r="I65" s="17"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="8"/>
+      <c r="I65" s="8"/>
     </row>
     <row r="66" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="18" t="s">
+      <c r="A66" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B66" s="17"/>
-      <c r="C66" s="17"/>
-      <c r="D66" s="17"/>
-      <c r="E66" s="17"/>
-      <c r="F66" s="17"/>
-      <c r="G66" s="17"/>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="8"/>
+      <c r="I66" s="8"/>
     </row>
     <row r="67" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="68" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="16" t="s">
+      <c r="A68" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="B68" s="17"/>
-      <c r="C68" s="17"/>
-      <c r="D68" s="17"/>
-      <c r="E68" s="17"/>
-      <c r="F68" s="17"/>
-      <c r="G68" s="17"/>
-      <c r="H68" s="17"/>
-      <c r="I68" s="17"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8"/>
+      <c r="I68" s="8"/>
     </row>
     <row r="69" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="18" t="s">
+      <c r="A69" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B69" s="17"/>
-      <c r="C69" s="17"/>
-      <c r="D69" s="17"/>
-      <c r="E69" s="17"/>
-      <c r="F69" s="17"/>
-      <c r="G69" s="17"/>
-      <c r="H69" s="17"/>
-      <c r="I69" s="17"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="8"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="8"/>
+      <c r="I69" s="8"/>
     </row>
     <row r="70" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="18" t="s">
+      <c r="A70" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B70" s="17"/>
-      <c r="C70" s="17"/>
-      <c r="D70" s="17"/>
-      <c r="E70" s="17"/>
-      <c r="F70" s="17"/>
-      <c r="G70" s="17"/>
-      <c r="H70" s="17"/>
-      <c r="I70" s="17"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="8"/>
     </row>
     <row r="71" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="18" t="s">
+      <c r="A71" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B71" s="17"/>
-      <c r="C71" s="17"/>
-      <c r="D71" s="17"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="17"/>
-      <c r="G71" s="17"/>
-      <c r="H71" s="17"/>
-      <c r="I71" s="17"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="8"/>
     </row>
     <row r="72" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="18" t="s">
+      <c r="A72" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B72" s="17"/>
-      <c r="C72" s="17"/>
-      <c r="D72" s="17"/>
-      <c r="E72" s="17"/>
-      <c r="F72" s="17"/>
-      <c r="G72" s="17"/>
-      <c r="H72" s="17"/>
-      <c r="I72" s="17"/>
+      <c r="B72" s="8"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="8"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="8"/>
     </row>
     <row r="73" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="18" t="s">
+      <c r="A73" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B73" s="17"/>
-      <c r="C73" s="17"/>
-      <c r="D73" s="17"/>
-      <c r="E73" s="17"/>
-      <c r="F73" s="17"/>
-      <c r="G73" s="17"/>
-      <c r="H73" s="17"/>
-      <c r="I73" s="17"/>
+      <c r="B73" s="8"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="8"/>
+      <c r="F73" s="8"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="8"/>
+      <c r="I73" s="8"/>
     </row>
     <row r="74" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="18" t="s">
+      <c r="A74" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B74" s="17"/>
-      <c r="C74" s="17"/>
-      <c r="D74" s="17"/>
-      <c r="E74" s="17"/>
-      <c r="F74" s="17"/>
-      <c r="G74" s="17"/>
-      <c r="H74" s="17"/>
-      <c r="I74" s="17"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
     </row>
     <row r="75" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="76" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="16" t="s">
+      <c r="A76" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="B76" s="17"/>
-      <c r="C76" s="17"/>
-      <c r="D76" s="17"/>
-      <c r="E76" s="17"/>
-      <c r="F76" s="17"/>
-      <c r="G76" s="17"/>
-      <c r="H76" s="17"/>
-      <c r="I76" s="17"/>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8"/>
     </row>
     <row r="77" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="18" t="s">
+      <c r="A77" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B77" s="17"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="17"/>
-      <c r="F77" s="17"/>
-      <c r="G77" s="17"/>
-      <c r="H77" s="17"/>
-      <c r="I77" s="17"/>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="8"/>
     </row>
     <row r="78" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="18" t="s">
+      <c r="A78" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B78" s="17"/>
-      <c r="C78" s="17"/>
-      <c r="D78" s="17"/>
-      <c r="E78" s="17"/>
-      <c r="F78" s="17"/>
-      <c r="G78" s="17"/>
-      <c r="H78" s="17"/>
-      <c r="I78" s="17"/>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="18" t="s">
+      <c r="A79" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B79" s="17"/>
-      <c r="C79" s="17"/>
-      <c r="D79" s="17"/>
-      <c r="E79" s="17"/>
-      <c r="F79" s="17"/>
-      <c r="G79" s="17"/>
-      <c r="H79" s="17"/>
-      <c r="I79" s="17"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
     </row>
     <row r="80" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="177">
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="A53:I53"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="C51:F51"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C48:F48"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="C56:F56"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C43:F43"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="G61:H61"/>
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="A63:I63"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C47:F47"/>
+    <mergeCell ref="C44:F44"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A78:I78"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C57:F57"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="C58:F58"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C45:F45"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A66:I66"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C42:F42"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="C61:F61"/>
     <mergeCell ref="A73:I73"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="G47:H47"/>
@@ -2411,159 +2576,6 @@
     <mergeCell ref="C55:F55"/>
     <mergeCell ref="G55:H55"/>
     <mergeCell ref="G29:H29"/>
-    <mergeCell ref="A64:I64"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A66:I66"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C49:F49"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C42:F42"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="A69:I69"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A78:I78"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A65:I65"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C57:F57"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="C58:F58"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C45:F45"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A76:I76"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="A63:I63"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="A77:I77"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="C40:F40"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C47:F47"/>
-    <mergeCell ref="C44:F44"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="A79:I79"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="G61:H61"/>
-    <mergeCell ref="A74:I74"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A71:I71"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C41:F41"/>
-    <mergeCell ref="C50:F50"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="C56:F56"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C43:F43"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="A53:I53"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="C51:F51"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C48:F48"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="C52:F52"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C60:F60"/>
-    <mergeCell ref="A60:B60"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup paperSize="9" scale="90" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -2583,58 +2595,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="25"/>
+      <c r="B1" s="29"/>
     </row>
     <row r="3" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="B3" s="23"/>
+      <c r="B3" s="22"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B4" s="23"/>
+      <c r="B4" s="22"/>
     </row>
     <row r="6" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="23"/>
+      <c r="B6" s="22"/>
     </row>
     <row r="7" spans="1:2" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="B7" s="23"/>
+      <c r="B7" s="22"/>
     </row>
     <row r="9" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="B9" s="23"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="26" t="s">
+      <c r="B9" s="22"/>
+    </row>
+    <row r="10" spans="1:2" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="B10" s="23"/>
+      <c r="B10" s="22"/>
     </row>
     <row r="12" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="B12" s="23"/>
+      <c r="B12" s="22"/>
     </row>
     <row r="13" spans="1:2" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="B13" s="23"/>
+      <c r="B13" s="22"/>
     </row>
     <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
@@ -2685,16 +2697,16 @@
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="B21" s="23"/>
+      <c r="B21" s="22"/>
     </row>
     <row r="22" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="B22" s="23"/>
+      <c r="B22" s="22"/>
     </row>
     <row r="23" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
@@ -2735,79 +2747,86 @@
       <c r="B27" s="2"/>
     </row>
     <row r="28" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="B28" s="12"/>
+      <c r="B28" s="15"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="B29" s="12"/>
+      <c r="B29" s="15"/>
     </row>
     <row r="30" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="B30" s="12"/>
+      <c r="B30" s="31"/>
     </row>
     <row r="31" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="B31" s="12"/>
+      <c r="B31" s="15"/>
     </row>
     <row r="32" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="B32" s="12"/>
+      <c r="B32" s="15"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="B33" s="12"/>
+      <c r="B33" s="15"/>
     </row>
     <row r="34" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="B34" s="12"/>
+      <c r="B34" s="15"/>
     </row>
     <row r="36" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="B36" s="23"/>
+      <c r="B36" s="22"/>
     </row>
     <row r="37" spans="1:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="26" t="s">
+      <c r="A37" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="B37" s="23"/>
+      <c r="B37" s="22"/>
     </row>
     <row r="39" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="B39" s="23"/>
+      <c r="B39" s="22"/>
     </row>
     <row r="40" spans="1:2" ht="46" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="27" t="s">
+      <c r="A40" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="B40" s="12"/>
+      <c r="B40" s="15"/>
     </row>
     <row r="41" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="27" t="s">
+      <c r="A41" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="B41" s="12"/>
+      <c r="B41" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A41:B41"/>
@@ -2824,16 +2843,9 @@
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.23622047244094491" bottom="0.23622047244094491" header="0.11811023622047245" footer="0.11811023622047245"/>
-  <pageSetup paperSize="9" scale="96" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.15" footer="0.15"/>
+  <pageSetup paperSize="9" scale="95" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>